--- a/02_mega_project_2_regulatory_capital/decision_engine/reports/notebook_04_workbook.xlsx
+++ b/02_mega_project_2_regulatory_capital/decision_engine/reports/notebook_04_workbook.xlsx
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Baseline: $9,756,908,313 ($9.76B); Adverse: $13,811,041,32 ($1.38B)3 (+41.6%); Severely Adverse: $20,536,046,97 ($2.05B)1 (+110.5%).</t>
+          <t>Baseline: $9,756,908,313 ($9.76B); Adverse: $13,811,041,323 ($13.81B) (+41.6%); Severely Adverse: $20,536,046,971 ($20.54B) (+110.5%).</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1221,12 +1221,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
